--- a/02-tailspin-civic-rev5-ato/artifacts/sctm_control_matrix.xlsx
+++ b/02-tailspin-civic-rev5-ato/artifacts/sctm_control_matrix.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'SCTM'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SCTM'!$A$1:$J$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SCTM'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Control Summary'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Summary'!$A$1:$C$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Legend'!$A$1:$B$8</definedName>
@@ -656,7 +656,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Service Provider Corporate</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Service Provider Corporate</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Service Provider System-Specific</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Service Provider Corporate</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Service Provider Corporate</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>Documented IR plan with defined severity tiers; 24x7 on-call rotation; US-CERT reporting procedure defined per FedRAMP requirements.</t>
+          <t>Documented IR plan with defined severity tiers; 24x7 on-call rotation; CISA reporting procedure defined per FedRAMP requirements.</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Service Provider Corporate</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>Internal reporting path defined; the one-hour US-CERT/FedRAMP ISSO notification requirement is documented but has not been exercised in a tabletop.</t>
+          <t>Internal reporting path defined; the one-hour CISA/agency ISSO notification requirement is documented but has not been exercised in a tabletop.</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
